--- a/Result/profitability/6902.xlsx
+++ b/Result/profitability/6902.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM19"/>
+  <dimension ref="A1:AM20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2843,6 +2843,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>6902</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>310</v>
+      </c>
+      <c r="D20" t="n">
+        <v>32</v>
+      </c>
+      <c r="E20" t="n">
+        <v>277</v>
+      </c>
+      <c r="F20" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="G20" t="n">
+        <v>64</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>20.58%</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J20" t="n">
+        <v>62</v>
+      </c>
+      <c r="K20" t="n">
+        <v>60</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="N20" t="n">
+        <v>88.99250000000001</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.05000000000000004</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.03048780487804881</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.519999999999996</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.005837449483610202</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>-8.347826086956522</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.819999999999993</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.0207336523125996</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK20" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
